--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486785_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486785_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7527</v>
+        <v>5.1141</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1569</v>
+        <v>2.419</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5958</v>
+        <v>2.6951</v>
       </c>
       <c r="G2" t="n">
         <v>4.4658</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6784</v>
+        <v>-0.3171</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1313</v>
+        <v>-0.8693</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4528</v>
+        <v>0.5522</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>E. AMANDIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4032</v>
+        <v>3.5677</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0891</v>
+        <v>0.9757</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3141</v>
+        <v>2.592</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0059</v>
+        <v>1.9207</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7377</v>
+        <v>1.6697</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2682</v>
+        <v>0.2509</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5858</v>
+        <v>1.0805</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3243</v>
+        <v>1.8084</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2615</v>
+        <v>-0.7279</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4201</v>
+        <v>0.8401</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4134</v>
+        <v>-0.1387</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0068</v>
+        <v>0.9788</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1819</v>
+        <v>-0.2757</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4966</v>
+        <v>-0.6761</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3147</v>
+        <v>0.4004</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. AMANDIO</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1815</v>
+        <v>3.4611</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7137</v>
+        <v>2.296</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4679</v>
+        <v>1.1651</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9207</v>
+        <v>3.0059</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6697</v>
+        <v>1.7377</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2509</v>
+        <v>1.2682</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0805</v>
+        <v>2.5858</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8084</v>
+        <v>1.3243</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7279</v>
+        <v>1.2615</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8401</v>
+        <v>0.4201</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1387</v>
+        <v>0.4134</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9788</v>
+        <v>0.0068</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6619</v>
+        <v>-0.1241</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9381</v>
+        <v>-0.2898</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2762</v>
+        <v>0.1657</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0345</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5081</v>
+        <v>0.1978</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5264</v>
+        <v>0.4519</v>
       </c>
       <c r="G5" t="n">
         <v>0.3492</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5848</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3032</v>
+        <v>-0.0071</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2815</v>
+        <v>0.2071</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2856</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4155</v>
+        <v>0.1356</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0639</v>
+        <v>-0.319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4794</v>
+        <v>0.4546</v>
       </c>
       <c r="G6" t="n">
         <v>0.2114</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3971</v>
+        <v>0.1172</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2756</v>
+        <v>0.0205</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1216</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1364</v>
+        <v>-0.3799</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-2.7854</v>
       </c>
       <c r="F7" t="n">
-        <v>1.019</v>
+        <v>2.4055</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0756</v>
+        <v>-0.3829</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7583</v>
+        <v>-2.2615</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6827</v>
+        <v>1.8786</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2756</v>
+        <v>-0.1261</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4138</v>
+        <v>-1.4328</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6895</v>
+        <v>1.3067</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3513</v>
+        <v>-0.2567</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3445</v>
+        <v>-0.8286</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0068</v>
+        <v>0.5719</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1931</v>
+        <v>2.3169</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8331</v>
+        <v>-0.4757</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3584</v>
+        <v>-0.821</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4747</v>
+        <v>0.3453</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALDERREY PULIDO</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3666</v>
+        <v>-0.4759</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3258</v>
+        <v>-1.2963</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9591</v>
+        <v>0.8204</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3954</v>
+        <v>0.0756</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0341</v>
+        <v>0.7583</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4295</v>
+        <v>-0.6827</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2221</v>
+        <v>-0.2756</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0347</v>
+        <v>0.4138</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2569</v>
+        <v>-0.6895</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8268</v>
+        <v>0.3513</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.3445</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8274</v>
+        <v>0.0068</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0718</v>
+        <v>0.2207</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1383</v>
+        <v>-0.0553</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0665</v>
+        <v>0.276</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>J. VALDERREY PULIDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6708</v>
+        <v>-0.681</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1508</v>
+        <v>-2.7395</v>
       </c>
       <c r="F9" t="n">
-        <v>2.48</v>
+        <v>2.0585</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3829</v>
+        <v>-0.3954</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2615</v>
+        <v>0.0341</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8786</v>
+        <v>-0.4295</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1261</v>
+        <v>-1.2221</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4328</v>
+        <v>0.0347</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3067</v>
+        <v>-1.2569</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2567</v>
+        <v>0.8268</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8286</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5719</v>
+        <v>0.8274</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3169</v>
+        <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7667</v>
+        <v>-0.3862</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1865</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4198</v>
+        <v>0.1658</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8704</v>
+        <v>-0.7069</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6525</v>
+        <v>-1.9399</v>
       </c>
       <c r="F10" t="n">
-        <v>1.782</v>
+        <v>1.233</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4352</v>
+        <v>-0.4174</v>
       </c>
       <c r="H10" t="n">
-        <v>2.724</v>
+        <v>-0.1869</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7113</v>
+        <v>-0.2305</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3885</v>
+        <v>-0.2297</v>
       </c>
       <c r="K10" t="n">
-        <v>2.656</v>
+        <v>0.5727</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7325</v>
+        <v>-0.8024</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0467</v>
+        <v>-0.1877</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0679</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9788</v>
+        <v>0.5719</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.827</v>
+        <v>-2.1239</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3749</v>
+        <v>-0.2896</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.214</v>
+        <v>-0.8141</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8391</v>
+        <v>0.5245</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8415</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1676</v>
+        <v>-0.8126</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2019</v>
+        <v>-2.4456</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0343</v>
+        <v>1.633</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4174</v>
+        <v>4.4352</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1869</v>
+        <v>2.724</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2305</v>
+        <v>1.7113</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2297</v>
+        <v>3.3885</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5727</v>
+        <v>2.656</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8024</v>
+        <v>0.7325</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1877</v>
+        <v>1.0467</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7596000000000001</v>
+        <v>0.0679</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5719</v>
+        <v>0.9788</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1239</v>
+        <v>-4.827</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7502</v>
+        <v>-0.317</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0761</v>
+        <v>-1.0072</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3259</v>
+        <v>0.6901</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2277</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9078</v>
+        <v>-2.6554</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5445</v>
+        <v>-1.4411</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3633</v>
+        <v>-1.2143</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6139</v>
@@ -1390,13 +1390,13 @@
         <v>0.3862</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2593</v>
+        <v>-0.0069</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.138</v>
+        <v>-0.0346</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1213</v>
+        <v>0.0277</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9406</v>
+        <v>7.216500000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.3542</v>
+        <v>-7.0783</v>
       </c>
       <c r="F13" t="n">
-        <v>14.2947</v>
+        <v>14.2948</v>
       </c>
       <c r="G13" t="n">
         <v>11.6542</v>
@@ -1438,28 +1438,28 @@
         <v>8.274400000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>3.379700000000001</v>
+        <v>3.3797</v>
       </c>
       <c r="J13" t="n">
-        <v>9.458400000000001</v>
+        <v>9.458399999999999</v>
       </c>
       <c r="K13" t="n">
         <v>10.3506</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8923999999999999</v>
+        <v>-0.8923999999999997</v>
       </c>
       <c r="M13" t="n">
         <v>2.1959</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0762</v>
+        <v>-2.076200000000001</v>
       </c>
       <c r="O13" t="n">
         <v>4.2723</v>
       </c>
       <c r="P13" t="n">
-        <v>9.999999999948939e-05</v>
+        <v>0.0001000000000003776</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.5157</v>
@@ -1468,10 +1468,10 @@
         <v>13.5155</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9301</v>
+        <v>-1.6544</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.3817</v>
+        <v>-5.1059</v>
       </c>
       <c r="U13" t="n">
         <v>3.4515</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4819</v>
+        <v>3.6431</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8099</v>
+        <v>1.6031</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6719</v>
+        <v>2.04</v>
       </c>
       <c r="G14" t="n">
         <v>0.7257</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7215</v>
+        <v>0.8828</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3039</v>
+        <v>-0.5108</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0254</v>
+        <v>1.3935</v>
       </c>
       <c r="V14" t="n">
         <v>1.8415</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6009</v>
+        <v>3.0119</v>
       </c>
       <c r="E15" t="n">
         <v>2.0888</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5121</v>
+        <v>0.9231</v>
       </c>
       <c r="G15" t="n">
         <v>0.9155</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1216</v>
+        <v>0.2895</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1659</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0443</v>
+        <v>0.4554</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9765</v>
+        <v>0.2485</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2905</v>
+        <v>-1.9584</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2669</v>
+        <v>2.2069</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9526</v>
+        <v>0.8265</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5516</v>
+        <v>1.4142</v>
       </c>
       <c r="I16" t="n">
-        <v>0.599</v>
+        <v>-0.5877</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.6139</v>
+        <v>2.3243</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6546</v>
+        <v>3.2081</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0407</v>
+        <v>-0.8838</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3387</v>
+        <v>-1.4978</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.897</v>
+        <v>-1.7939</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5583</v>
+        <v>0.2961</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7723</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7723</v>
+        <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1567</v>
+        <v>0.3102</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3234</v>
+        <v>-0.4211</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8333</v>
+        <v>0.7313</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3464</v>
+        <v>0.2332</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6481</v>
+        <v>-0.6556</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9945</v>
+        <v>0.8888</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8265</v>
+        <v>-2.6769</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4142</v>
+        <v>-2.6271</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5877</v>
+        <v>-0.0497</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3243</v>
+        <v>-1.6486</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2081</v>
+        <v>-1.0405</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8838</v>
+        <v>-0.6081</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4978</v>
+        <v>-1.0283</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7939</v>
+        <v>-1.5867</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2961</v>
+        <v>0.5583</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5446</v>
+        <v>1.5446</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4081</v>
+        <v>0.1378</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1108</v>
+        <v>-0.2347</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5189</v>
+        <v>0.3725</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0867</v>
+        <v>-0.1743</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-1.2284</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7758</v>
+        <v>1.054</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6769</v>
+        <v>-1.4293</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6271</v>
+        <v>-1.1308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0497</v>
+        <v>-0.2985</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6486</v>
+        <v>-0.5659</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0405</v>
+        <v>-0.6473</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6081</v>
+        <v>0.0814</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0283</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5867</v>
+        <v>-0.4835</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5583</v>
+        <v>-0.3799</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1821</v>
+        <v>0.0965</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4416</v>
+        <v>-0.6624</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2595</v>
+        <v>0.7589</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7618</v>
+        <v>-0.4633</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.642</v>
+        <v>-1.5315</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8802</v>
+        <v>1.0683</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4293</v>
+        <v>-1.9526</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1308</v>
+        <v>-2.5516</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2985</v>
+        <v>0.599</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5659</v>
+        <v>-1.6139</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6473</v>
+        <v>-1.6546</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.3387</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4835</v>
+        <v>-0.897</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3799</v>
+        <v>0.5583</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.491</v>
+        <v>0.717</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0761</v>
+        <v>0.0824</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5851</v>
+        <v>0.6347</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7459</v>
+        <v>-1.3363</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6454</v>
+        <v>-0.3352</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1004</v>
+        <v>-1.0011</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2393</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2097</v>
+        <v>0.1999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6071</v>
+        <v>-0.2969</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3974</v>
+        <v>0.4968</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4554</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.4355</v>
+        <v>-4.8936</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.7859</v>
+        <v>-5.2688</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3504</v>
+        <v>0.3753</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8495</v>
@@ -2092,13 +2092,13 @@
         <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5627</v>
+        <v>-0.0207</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1865</v>
+        <v>-0.6694</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6238</v>
+        <v>0.6486</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.3162</v>
+        <v>-6.5204</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.3191</v>
+        <v>-7.0088</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0029</v>
+        <v>0.4885</v>
       </c>
       <c r="G22" t="n">
         <v>-4.9745</v>
@@ -2170,13 +2170,13 @@
         <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.789</v>
+        <v>0.0068</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.883</v>
+        <v>-0.5728</v>
       </c>
       <c r="U22" t="n">
-        <v>0.094</v>
+        <v>0.5795</v>
       </c>
       <c r="V22" t="n">
         <v>0.5712</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.940399999999999</v>
+        <v>-6.251200000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.2947</v>
+        <v>-14.2948</v>
       </c>
       <c r="F23" t="n">
-        <v>7.3543</v>
+        <v>8.043799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-11.6544</v>
@@ -2224,13 +2224,13 @@
         <v>-2.1959</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0762</v>
+        <v>2.076200000000001</v>
       </c>
       <c r="L23" t="n">
         <v>-4.2721</v>
       </c>
       <c r="M23" t="n">
-        <v>-9.458400000000001</v>
+        <v>-9.458399999999999</v>
       </c>
       <c r="N23" t="n">
         <v>-10.3509</v>
@@ -2248,13 +2248,13 @@
         <v>13.5155</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9302</v>
+        <v>2.6198</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.4515</v>
+        <v>-3.4516</v>
       </c>
       <c r="U23" t="n">
-        <v>5.3817</v>
+        <v>6.0712</v>
       </c>
       <c r="V23" t="n">
         <v>2.7836</v>
